--- a/校正件排程.xlsx
+++ b/校正件排程.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User2\Documents\Works\02 校正輔助工具\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7E35B9-2C15-4657-89EC-8669EAEE5417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0282D3D4-D0D8-4404-A067-FF4CE9585853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="691">
   <si>
     <t>校正日</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2770,6 +2770,14 @@
   </si>
   <si>
     <t>E260096A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E260224A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E250250A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4250,7 +4258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表2"/>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F283"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
@@ -7815,6 +7823,28 @@
       </c>
       <c r="C281" s="1" t="s">
         <v>688</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="3">
+        <v>46296</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="3">
+        <v>46296</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>

--- a/校正件排程.xlsx
+++ b/校正件排程.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User2\Documents\Works\02 校正輔助工具\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0282D3D4-D0D8-4404-A067-FF4CE9585853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454E1FCC-42AB-437C-A33F-1B30C22544AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
